--- a/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第一部分.xlsx
+++ b/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第一部分.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -65,13 +65,13 @@
     <t>Note</t>
   </si>
   <si>
-    <t>qwq</t>
+    <t>小妍</t>
   </si>
   <si>
     <t>hide</t>
   </si>
   <si>
-    <t>qwq_Default</t>
+    <t>小妍_normal</t>
   </si>
   <si>
     <t>呀哈喽</t>
@@ -95,7 +95,7 @@
     <t>choice(跳转到1003|jump(1003))&amp;choice(跳转到1006|jump(1006))&amp;choice(跳转到新剧本2|loadscript(第二部分,1000))</t>
   </si>
   <si>
-    <t>qwq_Angry</t>
+    <t>小妍_angry</t>
   </si>
   <si>
     <t>分支1，1003</t>
@@ -110,7 +110,7 @@
     <t>jump(1010)</t>
   </si>
   <si>
-    <t>qwq_Happy</t>
+    <t>小妍_smile</t>
   </si>
   <si>
     <t>分支2，1006</t>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>分支合并，1010</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>我在说话</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1063,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="14.6" customWidth="1"/>
@@ -1309,9 +1315,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>1011</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -1337,6 +1364,866 @@
     <row r="18" spans="1:1">
       <c r="A18">
         <v>1016</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
